--- a/companies.xlsx
+++ b/companies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\jobx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF06E8F-3C19-4536-91AA-965B1BA986FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FBF95B-D77D-4EF6-82D2-3B8D636844A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>companyName</t>
   </si>
@@ -37,19 +37,37 @@
   </si>
   <si>
     <t>Guillermo Rauch</t>
+  </si>
+  <si>
+    <t>supabase</t>
+  </si>
+  <si>
+    <t>Paul Copplestone</t>
+  </si>
+  <si>
+    <t>juspay</t>
+  </si>
+  <si>
+    <t>vimal kumar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF001D35"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -72,8 +90,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -354,7 +373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -379,7 +398,24 @@
         <v>3</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/companies.xlsx
+++ b/companies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\jobx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FBF95B-D77D-4EF6-82D2-3B8D636844A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53C0199-23EA-4A4C-8EDF-36C50A027658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>companyName</t>
   </si>
@@ -33,22 +33,16 @@
     <t>founderName</t>
   </si>
   <si>
-    <t>vercel</t>
-  </si>
-  <si>
-    <t>Guillermo Rauch</t>
-  </si>
-  <si>
-    <t>supabase</t>
-  </si>
-  <si>
-    <t>Paul Copplestone</t>
-  </si>
-  <si>
-    <t>juspay</t>
-  </si>
-  <si>
-    <t>vimal kumar</t>
+    <t>lithouse</t>
+  </si>
+  <si>
+    <t>YASH Hegde</t>
+  </si>
+  <si>
+    <t>vedanta</t>
+  </si>
+  <si>
+    <t>yash hegde</t>
   </si>
 </sst>
 </file>
@@ -373,7 +367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -406,14 +400,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
